--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_59_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_59_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
         <v>19</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>27</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>10</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>7</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>88</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>31</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X35" t="n">
         <v>5</v>
@@ -4488,16 +4488,16 @@
         <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4684,16 +4684,16 @@
         <v>15</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>6</v>
@@ -4880,7 +4880,7 @@
         <v>16</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>4</v>
@@ -5468,7 +5468,7 @@
         <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>4</v>
@@ -6252,16 +6252,16 @@
         <v>8</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>2</v>
@@ -6784,16 +6784,16 @@
         <v>123</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_59_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_59_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>28.12</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -2178,11 +2178,11 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -2719,58 +2719,58 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>5</v>
-      </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -2915,14 +2915,14 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3307,10 +3307,10 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>4</v>
       </c>
       <c r="X35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -6264,14 +6264,14 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6796,14 +6796,14 @@
         <v>11</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="AA48" t="n">
